--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424E766E-5659-2A49-B4E7-9B065E74E7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD265218-70C4-644C-BA0E-B5DAA661A024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -393,6 +393,24 @@
   </si>
   <si>
     <t>us</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -731,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1493,10 +1511,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="C38">
         <f>((622 + 2*C32)/2*COS(C17*PI()/180) - C22)/SIN(C17*PI()/180)</f>
@@ -1521,63 +1539,63 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B46" t="s">
         <v>81</v>
@@ -1585,161 +1603,185 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="B50" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="B55" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>104</v>
-      </c>
-      <c r="B62" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>106</v>
-      </c>
-      <c r="B63" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="B64" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>109</v>
+        <v>104</v>
+      </c>
+      <c r="B65" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>110</v>
+        <v>106</v>
+      </c>
+      <c r="B66" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>113</v>
-      </c>
-      <c r="B69" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>115</v>
-      </c>
-      <c r="B70" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>118</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B75" t="s">
         <v>119</v>
       </c>
     </row>

--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD265218-70C4-644C-BA0E-B5DAA661A024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CCDDEF-1F30-9F41-AD47-DF8039672FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -1597,32 +1597,20 @@
       <c r="A46" t="s">
         <v>80</v>
       </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>82</v>
       </c>
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>83</v>
       </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>84</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CCDDEF-1F30-9F41-AD47-DF8039672FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426AA5F9-7C36-DD43-80F4-68D6662898E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -317,9 +317,6 @@
     <t>front_derailleur</t>
   </si>
   <si>
-    <t>adapter</t>
-  </si>
-  <si>
     <t>max_chainring_1x</t>
   </si>
   <si>
@@ -411,6 +408,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
         <v>120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>121</v>
       </c>
       <c r="C38">
         <f>((622 + 2*C32)/2*COS(C17*PI()/180) - C22)/SIN(C17*PI()/180)</f>
@@ -1539,18 +1539,18 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
         <v>122</v>
-      </c>
-      <c r="B39" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
         <v>124</v>
-      </c>
-      <c r="B40" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1651,53 +1651,59 @@
       <c r="A55" t="s">
         <v>93</v>
       </c>
-      <c r="B55" t="s">
-        <v>94</v>
+      <c r="B55" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
         <v>81</v>
@@ -1705,72 +1711,72 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>103</v>
+      </c>
+      <c r="B65" t="s">
         <v>104</v>
-      </c>
-      <c r="B65" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" t="s">
         <v>106</v>
-      </c>
-      <c r="B66" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" t="s">
         <v>113</v>
-      </c>
-      <c r="B72" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" t="s">
         <v>115</v>
-      </c>
-      <c r="B73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>117</v>
+      </c>
+      <c r="B75" t="s">
         <v>118</v>
-      </c>
-      <c r="B75" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426AA5F9-7C36-DD43-80F4-68D6662898E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DD5E53-64AA-8342-B464-A77356424FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>https://assets.specialized.com/i/specialized/91425-00_CRUX-SW-CYPRMET-GLDPRL_HERO-PDP?$scom-pdp-gallery-image$&amp;fmt=webp</t>
   </si>
 </sst>
 </file>
@@ -795,6 +798,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DD5E53-64AA-8342-B464-A77356424FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FFE818-4DA0-7241-8469-6B9D9ED4D5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.specialized.com/us/en/s-works-crux-sram-red-xplr/p/4223480?color=5381911-4223480</t>
-  </si>
-  <si>
     <t>17-Jul-2025</t>
   </si>
   <si>
@@ -414,6 +411,9 @@
   </si>
   <si>
     <t>https://assets.specialized.com/i/specialized/91425-00_CRUX-SW-CYPRMET-GLDPRL_HERO-PDP?$scom-pdp-gallery-image$&amp;fmt=webp</t>
+  </si>
+  <si>
+    <t>https://www.specialized.com/us/en/shop/bikes/gravel-bikes/crux</t>
   </si>
 </sst>
 </file>
@@ -787,7 +787,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -795,54 +795,54 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
       </c>
       <c r="C9">
         <v>165</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
       </c>
       <c r="C10">
         <v>380</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
       <c r="C11">
         <v>70</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12">
         <v>155</v>
@@ -943,10 +943,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13">
         <v>300</v>
@@ -969,10 +969,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
       </c>
       <c r="C14">
         <v>530</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
         <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
       </c>
       <c r="C15">
         <v>375</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
       </c>
       <c r="C17">
         <v>70.5</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
       </c>
       <c r="C18">
         <v>284</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19">
         <v>74</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
       <c r="C20">
         <v>74</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
       </c>
       <c r="C21">
         <v>401</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
         <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
       </c>
       <c r="C22">
         <v>50</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
         <v>48</v>
-      </c>
-      <c r="B23" t="s">
-        <v>49</v>
       </c>
       <c r="C23">
         <v>594</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
         <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
       </c>
       <c r="C24">
         <v>425</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
         <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
       </c>
       <c r="C25">
         <v>1008</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
         <v>54</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
       </c>
       <c r="C26">
         <v>512</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
         <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
       </c>
       <c r="C27">
         <v>749</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
         <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
       </c>
       <c r="C28">
         <v>466</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
         <v>60</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
       </c>
       <c r="C29">
         <v>75.5</v>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30">
         <v>725</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31">
         <v>700</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="1">
         <v>38</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>47</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34">
         <v>155</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35">
         <v>160.5</v>
@@ -1508,21 +1508,21 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" t="s">
         <v>68</v>
       </c>
-      <c r="B37" t="s">
-        <v>69</v>
-      </c>
       <c r="C37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" t="s">
         <v>119</v>
-      </c>
-      <c r="B38" t="s">
-        <v>120</v>
       </c>
       <c r="C38">
         <f>((622 + 2*C32)/2*COS(C17*PI()/180) - C22)/SIN(C17*PI()/180)</f>
@@ -1547,244 +1547,244 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" t="s">
         <v>121</v>
-      </c>
-      <c r="B39" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" t="s">
         <v>123</v>
-      </c>
-      <c r="B40" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" t="s">
         <v>70</v>
-      </c>
-      <c r="B41" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" t="s">
         <v>72</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" t="s">
         <v>74</v>
-      </c>
-      <c r="B43" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" t="s">
         <v>76</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" t="s">
         <v>78</v>
-      </c>
-      <c r="B45" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" t="s">
         <v>85</v>
-      </c>
-      <c r="B50" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" t="s">
         <v>87</v>
-      </c>
-      <c r="B51" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" t="s">
         <v>89</v>
-      </c>
-      <c r="B52" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" t="s">
         <v>103</v>
-      </c>
-      <c r="B65" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>104</v>
+      </c>
+      <c r="B66" t="s">
         <v>105</v>
-      </c>
-      <c r="B66" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" t="s">
         <v>112</v>
-      </c>
-      <c r="B72" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73" t="s">
         <v>114</v>
-      </c>
-      <c r="B73" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" t="s">
         <v>117</v>
-      </c>
-      <c r="B75" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FFE818-4DA0-7241-8469-6B9D9ED4D5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AD5097-72B3-244F-AFC9-DDD3570FCF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,9 +218,6 @@
     <t>Seat Tube Angle</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
     <t>wheel_size</t>
   </si>
   <si>
@@ -414,6 +411,9 @@
   </si>
   <si>
     <t>https://www.specialized.com/us/en/shop/bikes/gravel-bikes/crux</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
   </si>
 </sst>
 </file>
@@ -795,12 +795,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1384,8 +1384,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>61</v>
+      <c r="A30" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="F30">
         <v>725</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>700</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="1">
         <v>38</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33">
         <v>47</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34">
         <v>155</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35">
         <v>160.5</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" t="s">
         <v>67</v>
-      </c>
-      <c r="B37" t="s">
-        <v>68</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>41</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
         <v>118</v>
-      </c>
-      <c r="B38" t="s">
-        <v>119</v>
       </c>
       <c r="C38">
         <f>((622 + 2*C32)/2*COS(C17*PI()/180) - C22)/SIN(C17*PI()/180)</f>
@@ -1547,244 +1547,244 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" t="s">
         <v>120</v>
-      </c>
-      <c r="B39" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
         <v>122</v>
-      </c>
-      <c r="B40" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" t="s">
         <v>69</v>
-      </c>
-      <c r="B41" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
         <v>71</v>
-      </c>
-      <c r="B42" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
         <v>73</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
         <v>75</v>
-      </c>
-      <c r="B44" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" t="s">
         <v>77</v>
-      </c>
-      <c r="B45" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" t="s">
         <v>84</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" t="s">
         <v>86</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" t="s">
         <v>88</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>101</v>
+      </c>
+      <c r="B65" t="s">
         <v>102</v>
-      </c>
-      <c r="B65" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>103</v>
+      </c>
+      <c r="B66" t="s">
         <v>104</v>
-      </c>
-      <c r="B66" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" t="s">
         <v>111</v>
-      </c>
-      <c r="B72" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" t="s">
         <v>113</v>
-      </c>
-      <c r="B73" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75" t="s">
         <v>116</v>
-      </c>
-      <c r="B75" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AD5097-72B3-244F-AFC9-DDD3570FCF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D622BA3F-3454-2043-B0F7-0564F743878D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -383,9 +383,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -414,6 +411,15 @@
   </si>
   <si>
     <t>frame_weight</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Morgan Hill, California, USA</t>
   </si>
 </sst>
 </file>
@@ -752,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -795,12 +801,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1385,7 +1391,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F30">
         <v>725</v>
@@ -1519,10 +1525,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" t="s">
         <v>117</v>
-      </c>
-      <c r="B38" t="s">
-        <v>118</v>
       </c>
       <c r="C38">
         <f>((622 + 2*C32)/2*COS(C17*PI()/180) - C22)/SIN(C17*PI()/180)</f>
@@ -1547,18 +1553,18 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" t="s">
         <v>119</v>
-      </c>
-      <c r="B39" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" t="s">
         <v>121</v>
-      </c>
-      <c r="B40" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1693,7 +1699,7 @@
         <v>97</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -1701,7 +1707,7 @@
         <v>98</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -1783,8 +1789,16 @@
       <c r="A75" t="s">
         <v>115</v>
       </c>
-      <c r="B75" t="s">
-        <v>116</v>
+      <c r="B75" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized S-Works Crux 2025.xlsx
+++ b/data/gravel/Specialized S-Works Crux 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D622BA3F-3454-2043-B0F7-0564F743878D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E99DE1-5580-D144-BE3D-DF14F8088478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18720" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -420,6 +420,24 @@
   </si>
   <si>
     <t>Morgan Hill, California, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -758,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1645,159 +1663,189 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>91</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>98</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
-      </c>
-      <c r="B66" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>97</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+      <c r="B70" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="B71" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>112</v>
-      </c>
-      <c r="B73" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>115</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>128</v>
       </c>
     </row>
